--- a/Config/Translation_pathway.xlsx
+++ b/Config/Translation_pathway.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PhD\Data\SInAS workflow - native and alien\v7\Config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PhD\1. Data paper\SInAS-dataset_final_v5 - 3.2\SInAS-workflow_update\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1E1B046-4076-4AF3-924F-47BFA5D0CFFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F0A231E-19ED-4BAC-8BF2-7A266363C17E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="81">
   <si>
     <t>origTerm</t>
   </si>
@@ -244,6 +244,30 @@
   </si>
   <si>
     <t>Fur Farming</t>
+  </si>
+  <si>
+    <t>ship</t>
+  </si>
+  <si>
+    <t>unaided secondary natural dispersal</t>
+  </si>
+  <si>
+    <t>pilgrims</t>
+  </si>
+  <si>
+    <t>aircraft</t>
+  </si>
+  <si>
+    <t>boats</t>
+  </si>
+  <si>
+    <t>railway</t>
+  </si>
+  <si>
+    <t>plane</t>
+  </si>
+  <si>
+    <t>ground transport</t>
   </si>
 </sst>
 </file>
@@ -592,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B69"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.44140625"/>
@@ -945,69 +969,133 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>79</v>
+      </c>
+      <c r="B57" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>76</v>
+      </c>
+      <c r="B58" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>73</v>
+      </c>
+      <c r="B59" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>77</v>
+      </c>
+      <c r="B60" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>40</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B61" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B58" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B59" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B60" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B61" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>75</v>
+      </c>
+      <c r="B66" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B67" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>80</v>
+      </c>
+      <c r="B69" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B65" t="s">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>78</v>
+      </c>
+      <c r="B70" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B71" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B72" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B66" t="s">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B73" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B67" t="s">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B74" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B68" t="s">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B75" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B69" t="s">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B76" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>74</v>
+      </c>
+      <c r="B77" t="s">
         <v>53</v>
       </c>
     </row>
